--- a/tools/importer/reports/import-section-landing.report.xlsx
+++ b/tools/importer/reports/import-section-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-03-27T01:06:18.069Z</t>
+    <t>2026-04-01T07:36:36.516Z</t>
   </si>
   <si>
     <t>Tennis NSW | The governing body of Tennis in New South Wales</t>
@@ -73,7 +73,7 @@
     <t>section-landing</t>
   </si>
   <si>
-    <t>2026-03-27T01:07:59.084Z</t>
+    <t>2026-04-01T08:01:59.224Z</t>
   </si>
   <si>
     <t>About Us | Tennis NSW</t>
@@ -88,7 +88,7 @@
     <t>nsw/clubs</t>
   </si>
   <si>
-    <t>2026-03-27T01:07:44.304Z</t>
+    <t>2026-04-01T08:01:43.787Z</t>
   </si>
   <si>
     <t>Clubs | Tennis NSW</t>
@@ -112,7 +112,7 @@
     <t>nsw/our-work</t>
   </si>
   <si>
-    <t>2026-03-27T01:07:54.557Z</t>
+    <t>2026-04-01T08:01:53.285Z</t>
   </si>
   <si>
     <t>Our Work | Tennis NSW</t>
@@ -127,7 +127,7 @@
     <t>nsw/players</t>
   </si>
   <si>
-    <t>2026-03-27T01:07:49.332Z</t>
+    <t>2026-04-01T08:01:47.511Z</t>
   </si>
   <si>
     <t>Play | Tennis NSW</t>

--- a/tools/importer/reports/import-section-landing.report.xlsx
+++ b/tools/importer/reports/import-section-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-01T07:36:36.516Z</t>
+    <t>2026-04-02T06:11:05.694Z</t>
   </si>
   <si>
     <t>Tennis NSW | The governing body of Tennis in New South Wales</t>
@@ -73,7 +73,7 @@
     <t>section-landing</t>
   </si>
   <si>
-    <t>2026-04-01T08:01:59.224Z</t>
+    <t>2026-04-02T07:13:02.390Z</t>
   </si>
   <si>
     <t>About Us | Tennis NSW</t>
@@ -127,7 +127,7 @@
     <t>nsw/players</t>
   </si>
   <si>
-    <t>2026-04-01T08:01:47.511Z</t>
+    <t>2026-04-02T07:12:57.410Z</t>
   </si>
   <si>
     <t>Play | Tennis NSW</t>

--- a/tools/importer/reports/import-section-landing.report.xlsx
+++ b/tools/importer/reports/import-section-landing.report.xlsx
@@ -88,7 +88,7 @@
     <t>nsw/clubs</t>
   </si>
   <si>
-    <t>2026-04-01T08:01:43.787Z</t>
+    <t>2026-04-02T07:29:12.200Z</t>
   </si>
   <si>
     <t>Clubs | Tennis NSW</t>
@@ -112,7 +112,7 @@
     <t>nsw/our-work</t>
   </si>
   <si>
-    <t>2026-04-01T08:01:53.285Z</t>
+    <t>2026-04-02T07:29:17.215Z</t>
   </si>
   <si>
     <t>Our Work | Tennis NSW</t>

--- a/tools/importer/reports/import-section-landing.report.xlsx
+++ b/tools/importer/reports/import-section-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-02T06:11:05.694Z</t>
+    <t>2026-04-02T07:40:19.934Z</t>
   </si>
   <si>
     <t>Tennis NSW | The governing body of Tennis in New South Wales</t>
@@ -73,7 +73,7 @@
     <t>section-landing</t>
   </si>
   <si>
-    <t>2026-04-02T07:13:02.390Z</t>
+    <t>2026-04-02T07:40:40.209Z</t>
   </si>
   <si>
     <t>About Us | Tennis NSW</t>
@@ -88,7 +88,7 @@
     <t>nsw/clubs</t>
   </si>
   <si>
-    <t>2026-04-02T07:29:12.200Z</t>
+    <t>2026-04-02T07:40:24.270Z</t>
   </si>
   <si>
     <t>Clubs | Tennis NSW</t>
@@ -112,7 +112,7 @@
     <t>nsw/our-work</t>
   </si>
   <si>
-    <t>2026-04-02T07:29:17.215Z</t>
+    <t>2026-04-02T07:40:34.512Z</t>
   </si>
   <si>
     <t>Our Work | Tennis NSW</t>
@@ -127,7 +127,7 @@
     <t>nsw/players</t>
   </si>
   <si>
-    <t>2026-04-02T07:12:57.410Z</t>
+    <t>2026-04-02T07:40:29.815Z</t>
   </si>
   <si>
     <t>Play | Tennis NSW</t>
